--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_239_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_239_R24.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.578</v>
+        <v>6.5588</v>
       </c>
       <c r="E2" t="n">
-        <v>7.22</v>
+        <v>6.7049</v>
       </c>
       <c r="F2" t="n">
-        <v>0.358</v>
+        <v>-0.1461</v>
       </c>
       <c r="G2" t="n">
         <v>3.0129</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8692</v>
+        <v>0.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7512</v>
+        <v>0.2361</v>
       </c>
       <c r="U2" t="n">
-        <v>1.118</v>
+        <v>0.6139</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>C. PAYNE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6922</v>
+        <v>5.2535</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6096</v>
+        <v>6.003</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9174</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3385</v>
+        <v>5.4693</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4693</v>
+        <v>0.059</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1308</v>
+        <v>5.4103</v>
       </c>
       <c r="J3" t="n">
-        <v>2.533</v>
+        <v>7.5567</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2385</v>
+        <v>1.1427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2944</v>
+        <v>6.414</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1944</v>
+        <v>-2.0874</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7692</v>
+        <v>-1.0838</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4252</v>
+        <v>-1.0037</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6578</v>
+        <v>-0.3086</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3239</v>
+        <v>-0.3064</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3339</v>
+        <v>-0.0022</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>0.7886</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. PAYNE</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.238</v>
+        <v>3.3514</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1892</v>
+        <v>4.2688</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9512</v>
+        <v>-0.9174</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4693</v>
+        <v>0.3385</v>
       </c>
       <c r="H4" t="n">
-        <v>0.059</v>
+        <v>1.4693</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4103</v>
+        <v>-1.1308</v>
       </c>
       <c r="J4" t="n">
-        <v>7.5567</v>
+        <v>2.533</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1427</v>
+        <v>2.2385</v>
       </c>
       <c r="L4" t="n">
-        <v>6.414</v>
+        <v>0.2944</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0874</v>
+        <v>-2.1944</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0838</v>
+        <v>-0.7692</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0037</v>
+        <v>-1.4252</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3241</v>
+        <v>1.317</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1202</v>
+        <v>0.9831</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2038</v>
+        <v>0.3339</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7886</v>
+        <v>0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4658</v>
+        <v>2.2469</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1197</v>
+        <v>0.4303</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3461</v>
+        <v>1.8166</v>
       </c>
       <c r="G5" t="n">
         <v>2.6771</v>
@@ -844,13 +844,13 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1933</v>
+        <v>0.5878</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1221</v>
+        <v>0.4327</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3154</v>
+        <v>0.1551</v>
       </c>
       <c r="V5" t="n">
         <v>0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.443</v>
+        <v>0.447</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4281</v>
+        <v>0.193</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0149</v>
+        <v>0.254</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0658</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.666</v>
+        <v>0.224</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7468</v>
+        <v>-0.1256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0808</v>
+        <v>0.3497</v>
       </c>
       <c r="V6" t="n">
         <v>2.1444</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. JEKIRI</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2425</v>
+        <v>-0.997</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0206</v>
+        <v>-1.8193</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2218</v>
+        <v>0.8224</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6911</v>
+        <v>-1.9474</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3098</v>
+        <v>-2.2785</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3814</v>
+        <v>0.3311</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2382</v>
+        <v>-0.3965</v>
       </c>
       <c r="K7" t="n">
-        <v>0.091</v>
+        <v>-1.8885</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1472</v>
+        <v>1.492</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9294</v>
+        <v>-1.5509</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4008</v>
+        <v>-0.39</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5286</v>
+        <v>-1.1609</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.825</v>
+        <v>0.2546</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7591</v>
+        <v>-0.0312</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0659</v>
+        <v>0.2858</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5366</v>
+        <v>-1.7555</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5271</v>
+        <v>-2.123</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.3675</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9474</v>
+        <v>-4.2711</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2785</v>
+        <v>-0.6674</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3311</v>
+        <v>-3.6036</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3965</v>
+        <v>-1.1222</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8885</v>
+        <v>1.2134</v>
       </c>
       <c r="L9" t="n">
-        <v>1.492</v>
+        <v>-2.3357</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5509</v>
+        <v>-3.1488</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.39</v>
+        <v>-1.8809</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1609</v>
+        <v>-1.2679</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2851</v>
+        <v>0.1032</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7389</v>
+        <v>-0.1452</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4538</v>
+        <v>0.2484</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>T. JEKIRI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8389</v>
+        <v>-1.7844</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1727</v>
+        <v>-0.6969</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3339</v>
+        <v>-1.0874</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2711</v>
+        <v>-0.6911</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6674</v>
+        <v>-0.3098</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.6036</v>
+        <v>-0.3814</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1222</v>
+        <v>0.2382</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2134</v>
+        <v>0.091</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3357</v>
+        <v>0.1472</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1488</v>
+        <v>-0.9294</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8809</v>
+        <v>-0.4008</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2679</v>
+        <v>-0.5286</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9801</v>
+        <v>0.2831</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1949</v>
+        <v>0.0828</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2148</v>
+        <v>0.2003</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7886</v>
+        <v>-1.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2525</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4074</v>
+        <v>-4.6949</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1709</v>
+        <v>-5.0216</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.3267</v>
       </c>
       <c r="G11" t="n">
         <v>-5.5792</v>
@@ -1312,13 +1312,13 @@
         <v>3.2473</v>
       </c>
       <c r="S11" t="n">
-        <v>1.69</v>
+        <v>1.4025</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2363</v>
+        <v>0.3857</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4537</v>
+        <v>1.0168</v>
       </c>
       <c r="V11" t="n">
         <v>-1.214</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.022799999999999</v>
+        <v>7.143000000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>6.165800000000001</v>
+        <v>7.285900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1428</v>
+        <v>-0.1426999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4649</v>
+        <v>-2.464900000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.520700000000001</v>
+        <v>2.5207</v>
       </c>
       <c r="I12" t="n">
         <v>-4.9857</v>
@@ -1369,7 +1369,7 @@
         <v>8.3706</v>
       </c>
       <c r="L12" t="n">
-        <v>4.7833</v>
+        <v>4.783299999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-15.619</v>
@@ -1390,10 +1390,10 @@
         <v>19.7161</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5187</v>
+        <v>4.6389</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4743999999999998</v>
+        <v>1.5946</v>
       </c>
       <c r="U12" t="n">
         <v>3.0444</v>
@@ -1402,10 +1402,10 @@
         <v>2.6494</v>
       </c>
       <c r="W12" t="n">
-        <v>9.933399999999999</v>
+        <v>9.933400000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.284</v>
+        <v>-7.284000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.426</v>
+        <v>2.6276</v>
       </c>
       <c r="E13" t="n">
         <v>3.857</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4311</v>
+        <v>-1.2294</v>
       </c>
       <c r="G13" t="n">
         <v>3.5979</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2415</v>
+        <v>-1.0398</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4832</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7582</v>
+        <v>-0.5566</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3943</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5207</v>
+        <v>2.0997</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3705</v>
+        <v>1.9603</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1502</v>
+        <v>0.1394</v>
       </c>
       <c r="G14" t="n">
         <v>0.5996</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1357</v>
+        <v>0.4433</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1202</v>
+        <v>-0.5305</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9845</v>
+        <v>0.9737</v>
       </c>
       <c r="V14" t="n">
         <v>2.6805</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>G. PALATIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6757</v>
+        <v>0.232</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6943</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0186</v>
+        <v>0.232</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.502</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6088</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1108</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.053</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2639</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2109</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.555</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6551</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0154</v>
+        <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8011</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8707</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PALATIN</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.232</v>
+        <v>-0.0391</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.5524</v>
       </c>
       <c r="F16" t="n">
-        <v>0.232</v>
+        <v>0.5133</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.7246</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.9052</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.1806</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.822</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.1595</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.6625</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.0974</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.2543</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.8431</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.2998</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.2449</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.107</v>
+        <v>-0.4315</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7883</v>
+        <v>0.1609</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6813</v>
+        <v>-0.5925</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7246</v>
+        <v>-0.502</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9052</v>
+        <v>0.6088</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1806</v>
+        <v>-1.1108</v>
       </c>
       <c r="J17" t="n">
-        <v>1.822</v>
+        <v>1.053</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1595</v>
+        <v>1.2639</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6625</v>
+        <v>-0.2109</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0974</v>
+        <v>-1.555</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2543</v>
+        <v>-0.6551</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8431</v>
+        <v>-0.8999</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>3.0154</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3677</v>
+        <v>-0.1768</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2908</v>
+        <v>0.2677</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0769</v>
+        <v>-0.4446</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4464</v>
+        <v>-0.5343</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8823</v>
+        <v>0.6656</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3287</v>
+        <v>-1.1999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7702</v>
+        <v>-0.4473</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2341</v>
+        <v>-1.3206</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0043</v>
+        <v>0.8733</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2142</v>
+        <v>1.3255</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.215</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>2.4291</v>
+        <v>1.2479</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4439</v>
+        <v>-1.7729</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0191</v>
+        <v>-1.3983</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4248</v>
+        <v>-0.3746</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.358</v>
+        <v>-0.9425</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3655</v>
+        <v>-0.8017</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7235</v>
+        <v>-0.1408</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6468</v>
+        <v>-0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4254</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0955</v>
+        <v>-0.6816</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4297</v>
+        <v>0.8823</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5252</v>
+        <v>-1.5639</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4473</v>
+        <v>0.7702</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3206</v>
+        <v>-1.2341</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8733</v>
+        <v>2.0043</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3255</v>
+        <v>2.2142</v>
       </c>
       <c r="K19" t="n">
-        <v>0.07770000000000001</v>
+        <v>-0.215</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2479</v>
+        <v>2.4291</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7729</v>
+        <v>-1.4439</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3983</v>
+        <v>-1.0191</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3746</v>
+        <v>-0.4248</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5037</v>
+        <v>0.1228</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0376</v>
+        <v>-0.3655</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4661</v>
+        <v>0.4883</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5361</v>
+        <v>-0.6468</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0.4254</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3291</v>
+        <v>-1.5256</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0166</v>
+        <v>-0.3373</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3456</v>
+        <v>-1.1884</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4913</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7705</v>
+        <v>0.5739</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4208</v>
+        <v>0.067</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3497</v>
+        <v>0.507</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.061</v>
+        <v>-1.943</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1188</v>
+        <v>-2.0009</v>
       </c>
       <c r="F21" t="n">
         <v>0.0578</v>
@@ -2092,10 +2092,10 @@
         <v>2.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7038</v>
+        <v>-0.5858</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4753</v>
+        <v>-0.3574</v>
       </c>
       <c r="U21" t="n">
         <v>-0.2284</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8383</v>
+        <v>-5.0406</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5227</v>
+        <v>-3.815</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3156</v>
+        <v>-1.2256</v>
       </c>
       <c r="G22" t="n">
         <v>0.6607</v>
@@ -2170,13 +2170,13 @@
         <v>3.2473</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6254</v>
+        <v>-0.8276</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4936</v>
+        <v>-0.7859</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1318</v>
+        <v>-0.0417</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9304</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0229</v>
+        <v>-5.236400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8206000000000007</v>
+        <v>0.8205000000000005</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.8435</v>
+        <v>-6.0572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.465</v>
+        <v>2.464999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>-2.5208</v>
@@ -2227,7 +2227,7 @@
         <v>5.8501</v>
       </c>
       <c r="L23" t="n">
-        <v>9.769000000000002</v>
+        <v>9.769</v>
       </c>
       <c r="M23" t="n">
         <v>-13.1543</v>
@@ -2248,13 +2248,13 @@
         <v>17.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.5189</v>
+        <v>-2.7323</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0443</v>
+        <v>-3.0444</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4743999999999999</v>
+        <v>0.3120000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6494</v>
